--- a/smci/dist/20261025_美超微模型_v0.1.1.xlsx
+++ b/smci/dist/20261025_美超微模型_v0.1.1.xlsx
@@ -5179,7 +5179,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7318,7 +7318,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7517,7 +7517,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7638,7 +7638,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7759,7 +7759,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7880,7 +7880,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8001,7 +8001,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -36350,7 +36350,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/smci/dist/20261025_美超微模型_v0.1.1.xlsx
+++ b/smci/dist/20261025_美超微模型_v0.1.1.xlsx
@@ -6598,7 +6598,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -6617,7 +6617,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -36369,7 +36369,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -36388,7 +36388,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
   </si>
   <si>

--- a/smci/dist/20261025_美超微模型_v0.1.1.xlsx
+++ b/smci/dist/20261025_美超微模型_v0.1.1.xlsx
@@ -5160,26 +5160,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7299,26 +7299,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7498,26 +7498,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7619,26 +7619,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7740,26 +7740,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7861,26 +7861,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7982,26 +7982,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -36331,26 +36331,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
